--- a/MyPortfolio/public/tableau-competences.xlsx
+++ b/MyPortfolio/public/tableau-competences.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\degui\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AEF8744B-E537-4FCB-AC96-7C813F99152D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2B89C73B-624A-43DA-9CDB-3BEB3B947D8C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="11625" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Tableau de synthèse Épreuve E5" sheetId="1" r:id="rId1"/>
@@ -19,11 +19,6 @@
     <definedName name="_xlnm.Print_Area" localSheetId="0">'Tableau de synthèse Épreuve E5'!$A$1:$H$21</definedName>
   </definedNames>
   <calcPr calcId="0"/>
-  <extLst>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="1"/>
-    </ext>
-  </extLst>
 </workbook>
 </file>
 
@@ -46,9 +41,6 @@
   </si>
   <si>
     <t>▢ SISR</t>
-  </si>
-  <si>
-    <t>Adresse URL du portfolio :</t>
   </si>
   <si>
     <t>Compétences mises en œuvre
@@ -161,6 +153,9 @@
   </si>
   <si>
     <t>☑ SLAM</t>
+  </si>
+  <si>
+    <t>Adresse URL du portfolio : https://myportfoliomd.ddns.net</t>
   </si>
 </sst>
 </file>
@@ -691,6 +686,54 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -700,6 +743,9 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -734,57 +780,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1021,134 +1016,134 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:AQ77"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.86328125" defaultRowHeight="12.75" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="10.85546875" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="70.3984375" style="1" customWidth="1"/>
-    <col min="2" max="2" width="10.86328125" style="1" customWidth="1"/>
-    <col min="3" max="8" width="18.73046875" style="1" customWidth="1"/>
-    <col min="9" max="43" width="11.3984375" customWidth="1"/>
-    <col min="44" max="16384" width="10.86328125" style="1"/>
+    <col min="1" max="1" width="70.42578125" style="1" customWidth="1"/>
+    <col min="2" max="2" width="10.85546875" style="1" customWidth="1"/>
+    <col min="3" max="8" width="18.7109375" style="1" customWidth="1"/>
+    <col min="9" max="43" width="11.42578125" customWidth="1"/>
+    <col min="44" max="16384" width="10.85546875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:43" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="33" t="s">
+    <row r="1" spans="1:43" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="28" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="33"/>
-      <c r="C1" s="33"/>
-      <c r="D1" s="33"/>
-      <c r="E1" s="33"/>
-      <c r="F1" s="33"/>
-      <c r="G1" s="33" t="s">
+      <c r="B1" s="28"/>
+      <c r="C1" s="28"/>
+      <c r="D1" s="28"/>
+      <c r="E1" s="28"/>
+      <c r="F1" s="28"/>
+      <c r="G1" s="28" t="s">
         <v>1</v>
       </c>
-      <c r="H1" s="33"/>
-    </row>
-    <row r="2" spans="1:43" ht="41.1" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="33" t="s">
+      <c r="H1" s="28"/>
+    </row>
+    <row r="2" spans="1:43" ht="41.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2" s="28" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="33"/>
-      <c r="C2" s="33"/>
-      <c r="D2" s="33"/>
-      <c r="E2" s="33"/>
-      <c r="F2" s="33"/>
-      <c r="G2" s="33"/>
-      <c r="H2" s="33"/>
-    </row>
-    <row r="3" spans="1:43" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="47" t="s">
-        <v>35</v>
-      </c>
-      <c r="B3" s="34"/>
-      <c r="C3" s="34"/>
-      <c r="D3" s="34"/>
-      <c r="E3" s="35"/>
-      <c r="F3" s="36" t="s">
+      <c r="B2" s="28"/>
+      <c r="C2" s="28"/>
+      <c r="D2" s="28"/>
+      <c r="E2" s="28"/>
+      <c r="F2" s="28"/>
+      <c r="G2" s="28"/>
+      <c r="H2" s="28"/>
+    </row>
+    <row r="3" spans="1:43" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A3" s="29" t="s">
+        <v>34</v>
+      </c>
+      <c r="B3" s="30"/>
+      <c r="C3" s="30"/>
+      <c r="D3" s="30"/>
+      <c r="E3" s="31"/>
+      <c r="F3" s="32" t="s">
         <v>3</v>
       </c>
-      <c r="G3" s="34"/>
-      <c r="H3" s="37"/>
+      <c r="G3" s="30"/>
+      <c r="H3" s="33"/>
       <c r="K3" s="1"/>
       <c r="L3" s="1"/>
       <c r="M3" s="1"/>
     </row>
-    <row r="4" spans="1:43" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="48" t="s">
-        <v>36</v>
-      </c>
-      <c r="B4" s="21"/>
-      <c r="C4" s="21"/>
-      <c r="D4" s="21"/>
-      <c r="E4" s="22"/>
+    <row r="4" spans="1:43" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A4" s="37" t="s">
+        <v>35</v>
+      </c>
+      <c r="B4" s="38"/>
+      <c r="C4" s="38"/>
+      <c r="D4" s="38"/>
+      <c r="E4" s="39"/>
       <c r="F4" s="2" t="s">
         <v>4</v>
       </c>
       <c r="G4" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="H4" s="49" t="s">
+      <c r="H4" s="24" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="5" spans="1:43" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A5" s="40" t="s">
         <v>37</v>
       </c>
-    </row>
-    <row r="5" spans="1:43" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="23" t="s">
+      <c r="B5" s="41"/>
+      <c r="C5" s="41"/>
+      <c r="D5" s="41"/>
+      <c r="E5" s="41"/>
+      <c r="F5" s="41"/>
+      <c r="G5" s="41"/>
+      <c r="H5" s="42"/>
+    </row>
+    <row r="6" spans="1:43" ht="90" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A6" s="43" t="s">
         <v>6</v>
       </c>
-      <c r="B5" s="24"/>
-      <c r="C5" s="24"/>
-      <c r="D5" s="24"/>
-      <c r="E5" s="24"/>
-      <c r="F5" s="24"/>
-      <c r="G5" s="24"/>
-      <c r="H5" s="25"/>
-    </row>
-    <row r="6" spans="1:43" ht="90" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="26" t="s">
+      <c r="B6" s="45" t="s">
         <v>7</v>
       </c>
-      <c r="B6" s="28" t="s">
+      <c r="C6" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="C6" s="4" t="s">
+      <c r="D6" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="D6" s="4" t="s">
+      <c r="E6" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="E6" s="4" t="s">
+      <c r="F6" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="F6" s="4" t="s">
+      <c r="G6" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="G6" s="4" t="s">
+      <c r="H6" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="H6" s="5" t="s">
+    </row>
+    <row r="7" spans="1:43" s="6" customFormat="1" ht="324.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A7" s="44"/>
+      <c r="B7" s="46"/>
+      <c r="C7" s="7" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="7" spans="1:43" s="6" customFormat="1" ht="324.95" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="27"/>
-      <c r="B7" s="29"/>
-      <c r="C7" s="7" t="s">
+      <c r="D7" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="D7" s="7" t="s">
+      <c r="E7" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="E7" s="7" t="s">
+      <c r="F7" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="F7" s="7" t="s">
+      <c r="G7" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="G7" s="7" t="s">
+      <c r="H7" s="8" t="s">
         <v>19</v>
-      </c>
-      <c r="H7" s="8" t="s">
-        <v>20</v>
       </c>
       <c r="I7"/>
       <c r="J7"/>
@@ -1186,17 +1181,17 @@
       <c r="AP7"/>
       <c r="AQ7"/>
     </row>
-    <row r="8" spans="1:43" s="6" customFormat="1" ht="17.649999999999999" x14ac:dyDescent="0.35">
-      <c r="A8" s="30" t="s">
-        <v>21</v>
-      </c>
-      <c r="B8" s="31"/>
-      <c r="C8" s="31"/>
-      <c r="D8" s="31"/>
-      <c r="E8" s="31"/>
-      <c r="F8" s="31"/>
-      <c r="G8" s="31"/>
-      <c r="H8" s="32"/>
+    <row r="8" spans="1:43" s="6" customFormat="1" ht="18" x14ac:dyDescent="0.2">
+      <c r="A8" s="47" t="s">
+        <v>20</v>
+      </c>
+      <c r="B8" s="48"/>
+      <c r="C8" s="48"/>
+      <c r="D8" s="48"/>
+      <c r="E8" s="48"/>
+      <c r="F8" s="48"/>
+      <c r="G8" s="48"/>
+      <c r="H8" s="49"/>
       <c r="I8"/>
       <c r="J8"/>
       <c r="K8"/>
@@ -1233,15 +1228,15 @@
       <c r="AP8"/>
       <c r="AQ8"/>
     </row>
-    <row r="9" spans="1:43" s="6" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:43" s="6" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="9" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B9" s="10"/>
       <c r="C9" s="11"/>
       <c r="D9" s="11"/>
       <c r="E9" s="11" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F9" s="11"/>
       <c r="G9" s="11"/>
@@ -1282,13 +1277,13 @@
       <c r="AP9"/>
       <c r="AQ9"/>
     </row>
-    <row r="10" spans="1:43" s="6" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="41" t="s">
-        <v>32</v>
+    <row r="10" spans="1:43" s="6" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A10" s="18" t="s">
+        <v>31</v>
       </c>
       <c r="B10" s="10"/>
-      <c r="C10" s="43" t="s">
-        <v>27</v>
+      <c r="C10" s="20" t="s">
+        <v>26</v>
       </c>
       <c r="D10" s="11"/>
       <c r="E10" s="11"/>
@@ -1331,24 +1326,24 @@
       <c r="AP10"/>
       <c r="AQ10"/>
     </row>
-    <row r="11" spans="1:43" s="6" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="41" t="s">
-        <v>34</v>
+    <row r="11" spans="1:43" s="6" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A11" s="18" t="s">
+        <v>33</v>
       </c>
       <c r="B11" s="10"/>
       <c r="C11" s="11"/>
-      <c r="D11" s="43" t="s">
-        <v>27</v>
+      <c r="D11" s="20" t="s">
+        <v>26</v>
       </c>
       <c r="E11" s="11"/>
-      <c r="F11" s="43" t="s">
-        <v>27</v>
-      </c>
-      <c r="G11" s="43" t="s">
-        <v>27</v>
-      </c>
-      <c r="H11" s="42" t="s">
-        <v>27</v>
+      <c r="F11" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="G11" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="H11" s="19" t="s">
+        <v>26</v>
       </c>
       <c r="I11"/>
       <c r="J11"/>
@@ -1386,24 +1381,24 @@
       <c r="AP11"/>
       <c r="AQ11"/>
     </row>
-    <row r="12" spans="1:43" s="6" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="41" t="s">
-        <v>33</v>
+    <row r="12" spans="1:43" s="6" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A12" s="18" t="s">
+        <v>32</v>
       </c>
       <c r="B12" s="10"/>
       <c r="C12" s="11"/>
-      <c r="D12" s="43" t="s">
-        <v>27</v>
+      <c r="D12" s="20" t="s">
+        <v>26</v>
       </c>
       <c r="E12" s="11"/>
-      <c r="F12" s="43" t="s">
-        <v>27</v>
-      </c>
-      <c r="G12" s="43" t="s">
-        <v>27</v>
-      </c>
-      <c r="H12" s="42" t="s">
-        <v>27</v>
+      <c r="F12" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="G12" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="H12" s="19" t="s">
+        <v>26</v>
       </c>
       <c r="I12"/>
       <c r="J12"/>
@@ -1441,17 +1436,17 @@
       <c r="AP12"/>
       <c r="AQ12"/>
     </row>
-    <row r="13" spans="1:43" s="6" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A13" s="18" t="s">
-        <v>22</v>
-      </c>
-      <c r="B13" s="19"/>
-      <c r="C13" s="19"/>
-      <c r="D13" s="19"/>
-      <c r="E13" s="19"/>
-      <c r="F13" s="19"/>
-      <c r="G13" s="19"/>
-      <c r="H13" s="20"/>
+    <row r="13" spans="1:43" s="6" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A13" s="34" t="s">
+        <v>21</v>
+      </c>
+      <c r="B13" s="35"/>
+      <c r="C13" s="35"/>
+      <c r="D13" s="35"/>
+      <c r="E13" s="35"/>
+      <c r="F13" s="35"/>
+      <c r="G13" s="35"/>
+      <c r="H13" s="36"/>
       <c r="I13"/>
       <c r="J13"/>
       <c r="K13"/>
@@ -1488,22 +1483,22 @@
       <c r="AP13"/>
       <c r="AQ13"/>
     </row>
-    <row r="14" spans="1:43" s="6" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:43" s="6" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="9" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B14" s="10"/>
       <c r="C14" s="11"/>
       <c r="D14" s="11" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E14" s="11"/>
       <c r="F14" s="11" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G14" s="11"/>
       <c r="H14" s="12" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="I14"/>
       <c r="J14"/>
@@ -1541,17 +1536,17 @@
       <c r="AP14"/>
       <c r="AQ14"/>
     </row>
-    <row r="15" spans="1:43" s="6" customFormat="1" ht="17.649999999999999" x14ac:dyDescent="0.35">
-      <c r="A15" s="18" t="s">
-        <v>23</v>
-      </c>
-      <c r="B15" s="19"/>
-      <c r="C15" s="19"/>
-      <c r="D15" s="19"/>
-      <c r="E15" s="19"/>
-      <c r="F15" s="19"/>
-      <c r="G15" s="19"/>
-      <c r="H15" s="20"/>
+    <row r="15" spans="1:43" s="6" customFormat="1" ht="18" x14ac:dyDescent="0.2">
+      <c r="A15" s="34" t="s">
+        <v>22</v>
+      </c>
+      <c r="B15" s="35"/>
+      <c r="C15" s="35"/>
+      <c r="D15" s="35"/>
+      <c r="E15" s="35"/>
+      <c r="F15" s="35"/>
+      <c r="G15" s="35"/>
+      <c r="H15" s="36"/>
       <c r="J15"/>
       <c r="K15"/>
       <c r="L15"/>
@@ -1587,28 +1582,28 @@
       <c r="AP15"/>
       <c r="AQ15"/>
     </row>
-    <row r="16" spans="1:43" s="6" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:43" s="6" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="9" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B16" s="10"/>
       <c r="C16" s="11" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D16" s="11" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E16" s="11" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F16" s="11" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G16" s="11" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="H16" s="12" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="I16"/>
       <c r="J16"/>
@@ -1646,17 +1641,17 @@
       <c r="AP16"/>
       <c r="AQ16"/>
     </row>
-    <row r="17" spans="1:43" s="6" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A17" s="40" t="s">
-        <v>28</v>
-      </c>
-      <c r="B17" s="38"/>
-      <c r="C17" s="38"/>
-      <c r="D17" s="38"/>
-      <c r="E17" s="38"/>
-      <c r="F17" s="38"/>
-      <c r="G17" s="38"/>
-      <c r="H17" s="39"/>
+    <row r="17" spans="1:43" s="6" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A17" s="25" t="s">
+        <v>27</v>
+      </c>
+      <c r="B17" s="26"/>
+      <c r="C17" s="26"/>
+      <c r="D17" s="26"/>
+      <c r="E17" s="26"/>
+      <c r="F17" s="26"/>
+      <c r="G17" s="26"/>
+      <c r="H17" s="27"/>
       <c r="I17"/>
       <c r="J17"/>
       <c r="K17"/>
@@ -1693,9 +1688,9 @@
       <c r="AP17"/>
       <c r="AQ17"/>
     </row>
-    <row r="18" spans="1:43" s="6" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A18" s="41" t="s">
-        <v>29</v>
+    <row r="18" spans="1:43" s="6" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A18" s="18" t="s">
+        <v>28</v>
       </c>
       <c r="B18" s="10"/>
       <c r="C18" s="11"/>
@@ -1703,8 +1698,8 @@
       <c r="E18" s="11"/>
       <c r="F18" s="11"/>
       <c r="G18" s="11"/>
-      <c r="H18" s="42" t="s">
-        <v>27</v>
+      <c r="H18" s="19" t="s">
+        <v>26</v>
       </c>
       <c r="I18"/>
       <c r="J18"/>
@@ -1742,17 +1737,17 @@
       <c r="AP18"/>
       <c r="AQ18"/>
     </row>
-    <row r="19" spans="1:43" s="6" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A19" s="41" t="s">
-        <v>30</v>
+    <row r="19" spans="1:43" s="6" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A19" s="18" t="s">
+        <v>29</v>
       </c>
       <c r="B19" s="10"/>
       <c r="C19" s="11"/>
       <c r="D19" s="11"/>
       <c r="E19" s="11"/>
       <c r="F19" s="11"/>
-      <c r="G19" s="43" t="s">
-        <v>27</v>
+      <c r="G19" s="20" t="s">
+        <v>26</v>
       </c>
       <c r="H19" s="12"/>
       <c r="I19"/>
@@ -1791,22 +1786,22 @@
       <c r="AP19"/>
       <c r="AQ19"/>
     </row>
-    <row r="20" spans="1:43" s="6" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A20" s="44" t="s">
-        <v>31</v>
+    <row r="20" spans="1:43" s="6" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A20" s="21" t="s">
+        <v>30</v>
       </c>
       <c r="B20" s="13"/>
       <c r="C20" s="14"/>
       <c r="D20" s="14"/>
       <c r="E20" s="14"/>
-      <c r="F20" s="46" t="s">
-        <v>27</v>
-      </c>
-      <c r="G20" s="46" t="s">
-        <v>27</v>
-      </c>
-      <c r="H20" s="45" t="s">
-        <v>27</v>
+      <c r="F20" s="23" t="s">
+        <v>26</v>
+      </c>
+      <c r="G20" s="23" t="s">
+        <v>26</v>
+      </c>
+      <c r="H20" s="22" t="s">
+        <v>26</v>
       </c>
       <c r="I20"/>
       <c r="J20"/>
@@ -1844,7 +1839,7 @@
       <c r="AP20"/>
       <c r="AQ20"/>
     </row>
-    <row r="21" spans="1:43" s="6" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:43" s="6" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="15"/>
       <c r="B21" s="16"/>
       <c r="C21" s="17"/>
@@ -1889,7 +1884,7 @@
       <c r="AP21"/>
       <c r="AQ21"/>
     </row>
-    <row r="22" spans="1:43" s="6" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:43" s="6" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22"/>
       <c r="B22"/>
       <c r="C22"/>
@@ -1934,7 +1929,7 @@
       <c r="AP22"/>
       <c r="AQ22"/>
     </row>
-    <row r="23" spans="1:43" s="6" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:43" s="6" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A23"/>
       <c r="B23"/>
       <c r="C23"/>
@@ -1979,7 +1974,7 @@
       <c r="AP23"/>
       <c r="AQ23"/>
     </row>
-    <row r="24" spans="1:43" s="6" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:43" s="6" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24"/>
       <c r="B24"/>
       <c r="C24"/>
@@ -2024,7 +2019,7 @@
       <c r="AP24"/>
       <c r="AQ24"/>
     </row>
-    <row r="25" spans="1:43" s="6" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:43" s="6" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25"/>
       <c r="B25"/>
       <c r="C25"/>
@@ -2069,7 +2064,7 @@
       <c r="AP25"/>
       <c r="AQ25"/>
     </row>
-    <row r="26" spans="1:43" s="6" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:43" s="6" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26"/>
       <c r="B26"/>
       <c r="C26"/>
@@ -2114,7 +2109,7 @@
       <c r="AP26"/>
       <c r="AQ26"/>
     </row>
-    <row r="27" spans="1:43" s="6" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:43" s="6" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27"/>
       <c r="B27"/>
       <c r="C27"/>
@@ -2159,7 +2154,7 @@
       <c r="AP27"/>
       <c r="AQ27"/>
     </row>
-    <row r="28" spans="1:43" s="6" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:43" s="6" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28"/>
       <c r="B28"/>
       <c r="C28"/>
@@ -2204,7 +2199,7 @@
       <c r="AP28"/>
       <c r="AQ28"/>
     </row>
-    <row r="29" spans="1:43" s="6" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:43" s="6" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29"/>
       <c r="B29"/>
       <c r="C29"/>
@@ -2249,7 +2244,7 @@
       <c r="AP29"/>
       <c r="AQ29"/>
     </row>
-    <row r="30" spans="1:43" s="6" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:43" s="6" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30"/>
       <c r="B30"/>
       <c r="C30"/>
@@ -2294,7 +2289,7 @@
       <c r="AP30"/>
       <c r="AQ30"/>
     </row>
-    <row r="31" spans="1:43" s="6" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:43" s="6" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A31"/>
       <c r="B31"/>
       <c r="C31"/>
@@ -2339,43 +2334,43 @@
       <c r="AP31"/>
       <c r="AQ31"/>
     </row>
-    <row r="32" spans="1:43" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="33" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="34" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="35" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="36" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="37" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="38" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="39" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="40" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="41" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="42" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="43" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="44" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="45" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="46" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="47" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="48" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="49" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="50" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="51" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="52" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="53" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="54" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="55" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="56" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="57" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="58" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="59" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="60" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="61" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="62" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="63" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="64" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="65" spans="1:8" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="66" spans="1:8" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="67" spans="1:8" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="68" spans="1:8" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:43" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="33" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="34" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="35" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="36" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="37" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="38" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="39" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="40" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="41" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="42" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="43" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="44" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="45" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="46" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="47" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="48" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="49" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="50" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="51" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="52" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="54" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="55" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="56" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="57" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="58" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="59" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="60" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="61" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="62" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="63" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="64" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="65" spans="1:8" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="66" spans="1:8" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="67" spans="1:8" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="68" spans="1:8" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A68" s="1"/>
       <c r="B68" s="1"/>
       <c r="C68" s="1"/>
@@ -2385,7 +2380,7 @@
       <c r="G68" s="1"/>
       <c r="H68" s="1"/>
     </row>
-    <row r="69" spans="1:8" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:8" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A69" s="1"/>
       <c r="B69" s="1"/>
       <c r="C69" s="1"/>
@@ -2395,7 +2390,7 @@
       <c r="G69" s="1"/>
       <c r="H69" s="1"/>
     </row>
-    <row r="70" spans="1:8" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:8" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A70" s="1"/>
       <c r="B70" s="1"/>
       <c r="C70" s="1"/>
@@ -2405,7 +2400,7 @@
       <c r="G70" s="1"/>
       <c r="H70" s="1"/>
     </row>
-    <row r="71" spans="1:8" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:8" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A71" s="1"/>
       <c r="B71" s="1"/>
       <c r="C71" s="1"/>
@@ -2415,7 +2410,7 @@
       <c r="G71" s="1"/>
       <c r="H71" s="1"/>
     </row>
-    <row r="72" spans="1:8" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:8" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A72" s="1"/>
       <c r="B72" s="1"/>
       <c r="C72" s="1"/>
@@ -2425,7 +2420,7 @@
       <c r="G72" s="1"/>
       <c r="H72" s="1"/>
     </row>
-    <row r="73" spans="1:8" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:8" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A73" s="1"/>
       <c r="B73" s="1"/>
       <c r="C73" s="1"/>
@@ -2435,7 +2430,7 @@
       <c r="G73" s="1"/>
       <c r="H73" s="1"/>
     </row>
-    <row r="74" spans="1:8" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:8" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A74" s="1"/>
       <c r="B74" s="1"/>
       <c r="C74" s="1"/>
@@ -2445,7 +2440,7 @@
       <c r="G74" s="1"/>
       <c r="H74" s="1"/>
     </row>
-    <row r="75" spans="1:8" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:8" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A75" s="1"/>
       <c r="B75" s="1"/>
       <c r="C75" s="1"/>
@@ -2455,7 +2450,7 @@
       <c r="G75" s="1"/>
       <c r="H75" s="1"/>
     </row>
-    <row r="76" spans="1:8" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:8" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A76" s="1"/>
       <c r="B76" s="1"/>
       <c r="C76" s="1"/>
@@ -2465,7 +2460,7 @@
       <c r="G76" s="1"/>
       <c r="H76" s="1"/>
     </row>
-    <row r="77" spans="1:8" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:8" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A77" s="1"/>
       <c r="B77" s="1"/>
       <c r="C77" s="1"/>
